--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -737,7 +728,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>39.7</v>
+        <v>31.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>16.9</v>
@@ -767,7 +758,7 @@
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>28.8</v>
+        <v>21.1</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>91.2</v>
@@ -779,19 +770,19 @@
         <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>23.8</v>
+        <v>29.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>4.5</v>
+        <v>45.2</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.5</v>
+        <v>27.5</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
@@ -823,7 +814,7 @@
         <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>81.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>17.3</v>
@@ -838,16 +829,16 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>2</v>
+        <v>20.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
@@ -859,7 +850,7 @@
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>23.1</v>
+        <v>28.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>70.2</v>
@@ -877,7 +868,7 @@
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -900,10 +891,10 @@
         <v>32.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>27.6</v>
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15.2</v>
@@ -918,7 +909,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>17.4</v>
@@ -927,28 +918,28 @@
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>921.2</v>
+        <v>91.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>24.9</v>
+        <v>24.1</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>390.6</v>
+        <v>50.6</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>17.4</v>
+        <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>27.2</v>
@@ -960,7 +951,7 @@
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -979,7 +970,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="3" t="n">
         <v>30.5</v>
       </c>
       <c r="E7" s="3" t="n">
@@ -992,7 +983,7 @@
         <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1001,7 +992,7 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.2</v>
+        <v>15.8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.3</v>
@@ -1025,10 +1016,10 @@
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.2</v>
+        <v>87.2</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0.9</v>
@@ -1094,7 +1085,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>791.2</v>
+        <v>91.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
@@ -1127,7 +1118,7 @@
         <v>86.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>27.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1144,7 +1135,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>147.9</v>
+        <v>147.4</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1171,13 +1162,13 @@
         <v>92.59999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>3972.6</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.2</v>
+        <v>454.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1201,7 +1192,7 @@
         <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>11</v>
+        <v>110.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
@@ -1233,19 +1224,19 @@
         <v>17.9</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.3</v>
+        <v>23.7</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.6</v>
+        <v>19.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.1</v>
@@ -1257,10 +1248,10 @@
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>291.3</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
@@ -1275,7 +1266,7 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>6.4</v>
+        <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1287,13 +1278,13 @@
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>2.5</v>
+        <v>25.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>62.8</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1309,7 +1300,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="3" t="n">
         <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
@@ -1323,15 +1314,15 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>11.3</v>
+        <v>1.4</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <v>24.3</v>
+      <c r="M11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1340,13 +1331,13 @@
         <v>91.59999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>29.8</v>
+        <v>23.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>26.7</v>
@@ -1360,7 +1351,7 @@
       <c r="V11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="W11" s="8" t="n">
+      <c r="W11" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1396,64 +1387,64 @@
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>984.1</v>
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>1.9</v>
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>2.5</v>
+        <v>25.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>61.3</v>
+        <v>67.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1479,7 +1470,7 @@
         <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>89.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1488,22 +1479,22 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
@@ -1518,10 +1509,10 @@
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>14.2</v>
+        <v>74.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>31.8</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1533,10 +1524,10 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1552,7 +1543,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.5</v>
+        <v>10.1</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>29.9</v>
@@ -1564,10 +1555,10 @@
         <v>24.2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
@@ -1576,7 +1567,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1585,7 +1576,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1594,13 +1585,13 @@
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>31.4</v>
+        <v>27.7</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58.2</v>
@@ -1618,10 +1609,10 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>27.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>51.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1643,17 +1634,17 @@
       <c r="E15" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>93.5</v>
+      <c r="F15" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1668,7 +1659,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1677,13 +1668,13 @@
         <v>0.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>2.6</v>
+        <v>26.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>20.7</v>
+        <v>10.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1692,7 +1683,7 @@
         <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.4</v>
+        <v>21.4</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>20.9</v>
@@ -1701,10 +1692,10 @@
         <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>8.5</v>
+        <v>85.3</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1721,10 +1712,10 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="n">
-        <v>14</v>
+        <v>140.4</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>112.3</v>
+        <v>12.3</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>116.6</v>
@@ -1736,10 +1727,10 @@
         <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>29.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>17.3</v>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
@@ -1752,16 +1743,16 @@
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>853.2</v>
+        <v>153.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>127.2</v>
+        <v>129.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>122.3</v>
+        <v>182.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1770,19 +1761,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
+        <v>41.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>187.8</v>
+        <v>116.7</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>970.8</v>
+        <v>408.9</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1800,18 +1791,20 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D17" s="3" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1820,20 +1813,20 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>22.9</v>
+        <v>2.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
-        <v>19.9</v>
+      <c r="L17" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>22.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>91.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
@@ -1842,16 +1835,16 @@
         <v>25.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6.4</v>
+        <v>64.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>22.9</v>
@@ -1860,7 +1853,7 @@
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>82.2</v>
@@ -1895,7 +1888,7 @@
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1910,13 +1903,13 @@
         <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.3</v>
+        <v>19.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>291.2</v>
+        <v>91.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
@@ -1934,10 +1927,10 @@
         <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>21.8</v>
+        <v>121.8</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -1965,22 +1958,22 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2.4</v>
+        <v>24.1</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.5</v>
@@ -1995,10 +1988,10 @@
         <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
@@ -2016,22 +2009,22 @@
         <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.2</v>
+        <v>90.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>12.9</v>
+        <v>19.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2050,19 +2043,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="8" t="n">
-        <v>59.6</v>
+      <c r="G20" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2071,16 +2064,16 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="8" t="n">
-        <v>19.8</v>
+      <c r="L20" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
@@ -2090,19 +2083,19 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.6</v>
+        <v>26.2</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>29.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>22.8</v>
@@ -2110,8 +2103,8 @@
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="8" t="n">
-        <v>23.2</v>
+      <c r="X20" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2165,7 +2158,9 @@
       <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O21" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -2176,19 +2171,19 @@
         <v>19.2</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.3</v>
+        <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.7</v>
+        <v>28.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>19.1</v>
@@ -2197,7 +2192,7 @@
         <v>21.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.8</v>
@@ -2216,25 +2211,25 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2.3</v>
+        <v>23.2</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.2</v>
@@ -2243,37 +2238,37 @@
         <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.1</v>
+        <v>8.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>991.2</v>
+        <v>91.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.9</v>
+        <v>28.5</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>2.2</v>
+        <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>86.2</v>
+        <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>13.9</v>
+        <v>19.9</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>2.4</v>
+        <v>24.6</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>26.2</v>
@@ -2302,10 +2297,10 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>1942.6</v>
+        <v>147.6</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>112.2</v>
@@ -2314,28 +2309,28 @@
         <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.6</v>
+        <v>7.6</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>28.7</v>
+        <v>31.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1952.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>951.2</v>
+        <v>451.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
@@ -2345,13 +2340,13 @@
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.9</v>
+        <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>36</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>37.7</v>
+        <v>34.7</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>108.4</v>
@@ -2360,10 +2355,10 @@
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>198.7</v>
+        <v>117.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9425.6</v>
+        <v>427.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2382,7 +2377,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>28.5</v>
@@ -2405,11 +2400,11 @@
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <v>65.59999999999999</v>
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>98.8</v>
+        <v>18.8</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>18.6</v>
@@ -2418,7 +2413,7 @@
         <v>0.8</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.2</v>
@@ -2427,18 +2422,18 @@
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="8" t="n">
+      <c r="V24" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="W24" s="3" t="n">
@@ -2451,7 +2446,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2470,20 +2465,20 @@
       <c r="D25" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>444.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>34.4</v>
@@ -2492,19 +2487,19 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>12.9</v>
+        <v>19.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>59.2</v>
+        <v>92.2</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>2.6</v>
@@ -2516,10 +2511,10 @@
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>31.2</v>
+        <v>71.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>25.3</v>
@@ -2528,10 +2523,10 @@
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.9</v>
+        <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>69.3</v>
+        <v>67.2</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2548,25 +2543,25 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>111.6</v>
+        <v>1.1</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>29.6</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.4</v>
+        <v>18.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.6</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2577,14 +2572,14 @@
       <c r="L26" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M26" s="8" t="n">
-        <v>989.6</v>
+      <c r="M26" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>8.1</v>
+        <v>91.2</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2593,10 +2588,10 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.3</v>
+        <v>29.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2643,37 +2638,37 @@
         <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>922.2</v>
+        <v>98.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2682,7 +2677,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>63.2</v>
+        <v>0.1</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2716,17 +2711,17 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="3" t="n">
         <v>32.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2741,22 +2736,22 @@
         <v>0.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>14.8</v>
+        <v>18.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.9</v>
+        <v>30.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2765,19 +2760,19 @@
         <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>4</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>2.1</v>
+        <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>21.2</v>
+        <v>216.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2824,14 +2819,14 @@
         <v>0.5</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>0.1</v>
+        <v>9.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0</v>
@@ -2846,13 +2841,13 @@
         <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>12.2</v>
+        <v>72.2</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>13.4</v>
+        <v>19.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2864,7 +2859,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.1</v>
+        <v>20.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2881,22 +2876,22 @@
       </c>
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="n">
-        <v>1498.4</v>
+        <v>148.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>189.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>11.8</v>
+        <v>119.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.8</v>
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>17.8</v>
@@ -2905,10 +2900,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>292.5</v>
+        <v>92.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>392.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
@@ -2933,16 +2928,16 @@
         <v>118.2</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>104.1</v>
+        <v>104.6</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.2</v>
+        <v>372.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>52.4</v>
+        <v>32.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>33</v>
@@ -2965,32 +2960,32 @@
         <v>29.7</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>23.9</v>
+        <v>22.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.1</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>10.3</v>
+        <v>18.9</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>28.4</v>
+        <v>24</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -2999,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>22.6</v>
@@ -3017,10 +3012,10 @@
         <v>20.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>47.8</v>
+        <v>22.9</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>77.8</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>6.5</v>
@@ -3044,8 +3039,8 @@
       <c r="C32" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D32" s="8" t="n">
-        <v>232.8</v>
+      <c r="D32" s="3" t="n">
+        <v>32.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>4.5</v>
@@ -3054,7 +3049,7 @@
         <v>85</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>17.5</v>
@@ -3063,23 +3058,23 @@
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>29.9</v>
@@ -3091,13 +3086,13 @@
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>35.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.1</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>25.8</v>
@@ -3106,7 +3101,7 @@
         <v>85.3</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3123,19 +3118,19 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.4</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3150,14 +3145,14 @@
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>8</v>
+        <v>90.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3172,13 +3167,13 @@
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>7.8</v>
+        <v>48.2</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>24.2</v>
+        <v>26.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>27.4</v>
@@ -3187,7 +3182,7 @@
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>15</v>
@@ -3205,7 +3200,9 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D34" s="3" t="n">
         <v>32.1</v>
       </c>
@@ -3213,12 +3210,12 @@
         <v>19.4</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3237,16 +3234,16 @@
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.1</v>
+        <v>87.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3255,10 +3252,10 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>61.2</v>
+        <v>67.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3270,7 +3267,7 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>9</v>
@@ -3289,16 +3286,16 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>27.4</v>
+        <v>24.4</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>12</v>
@@ -3319,18 +3316,18 @@
         <v>19</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.1</v>
+        <v>28.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>28</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -3340,13 +3337,13 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>129.2</v>
+        <v>12.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>2.5</v>
+        <v>25.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
@@ -3358,7 +3355,7 @@
         <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>33.6</v>
+        <v>53.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3374,7 +3371,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="3" t="n">
         <v>33.6</v>
       </c>
       <c r="E36" s="3" t="n">
@@ -3384,7 +3381,7 @@
         <v>25.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
@@ -3402,28 +3399,28 @@
         <v>18.7</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.8</v>
+        <v>8.6</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <v>35</v>
+      <c r="R36" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>48.2</v>
+        <v>44.2</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>28.3</v>
@@ -3435,7 +3432,7 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>85.2</v>
+        <v>55.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>11.5</v>
@@ -3461,7 +3458,7 @@
         <v>161.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1929.5</v>
+        <v>92.5</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>126.9</v>
@@ -3479,52 +3476,52 @@
         <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>949.9</v>
+        <v>49.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>951.1</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.2</v>
+        <v>150.4</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>28.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>117.3</v>
+        <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.4</v>
+        <v>190.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101.3</v>
+        <v>70.3</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7367.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.3</v>
+        <v>247.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3541,13 +3538,13 @@
       </c>
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2.5</v>
+        <v>25.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3561,51 +3558,53 @@
       <c r="J38" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L38" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="R38" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>4.9</v>
+        <v>49.2</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>82.2</v>
+        <v>22.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>13.2</v>
+        <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3633,7 +3632,7 @@
       <c r="G39" s="3" t="n">
         <v>45.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3643,17 +3642,17 @@
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>49</v>
+        <v>6.2</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3665,7 +3664,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.1</v>
+        <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3677,7 +3676,7 @@
         <v>20.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>2.4</v>
+        <v>241</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
@@ -3711,19 +3710,19 @@
         <v>18.3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3732,10 +3731,10 @@
         <v>18.9</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>29.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3744,7 +3743,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.8</v>
+        <v>31.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3756,7 +3755,7 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
@@ -3771,7 +3770,7 @@
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>826.2</v>
+        <v>26.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3797,7 +3796,7 @@
         <v>25.4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>12.8</v>
+        <v>82.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3806,26 +3805,26 @@
         <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>9.1</v>
+      <c r="L41" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>29.4</v>
+        <v>24.1</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3834,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>37.8</v>
+        <v>59.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3846,13 +3845,13 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3879,25 +3878,25 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1.3</v>
+        <v>13.6</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>72.8</v>
+      <c r="J42" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3906,25 +3905,25 @@
         <v>0.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>2.5</v>
+        <v>25</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>11.6</v>
+        <v>14.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4025,7 +4024,7 @@
         <v>122.3</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>24.6</v>
+        <v>34.6</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>102</v>
@@ -4040,20 +4039,20 @@
         <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>111.4</v>
+        <v>14.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>111.9</v>
+        <v>11.1</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>2366.2</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
@@ -4068,25 +4067,25 @@
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>132.7</v>
+        <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1.8</v>
+        <v>96.3</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>892.7</v>
+        <v>85.7</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>19327.2</v>
+        <v>327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4103,13 +4102,13 @@
       </c>
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>32.3</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>25.5</v>
@@ -4118,28 +4117,28 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J46" s="8" t="n">
-        <v>30.7</v>
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.4</v>
+        <v>9.9</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>2.6</v>
+        <v>26.7</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>0.2</v>
@@ -4151,23 +4150,25 @@
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>22.8</v>
+        <v>29.8</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>2.4</v>
+        <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>992.9</v>
+        <v>298.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
